--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260612.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260612.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D53"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>27.32%</t>
+          <t>26.96%</t>
         </is>
       </c>
     </row>
@@ -638,112 +638,112 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.46%</t>
+          <t>9.42%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>MRVL US</t>
+          <t>GEV US</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Marvell Technology Inc</t>
+          <t>奇異維諾瓦公司</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>60,105</t>
+          <t>18,575</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.34%</t>
+          <t>7.56%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>GEV US</t>
+          <t>MRVL US</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>奇異維諾瓦公司</t>
+          <t>Marvell Technology Inc</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>18,575</t>
+          <t>60,105</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.33%</t>
+          <t>7.28%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>C_NTD</t>
+          <t>NEE US</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>CASH</t>
+          <t>NextEra Energy Inc</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>426,200,048</t>
+          <t>143,395</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.86%</t>
+          <t>5.34%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>NEE US</t>
+          <t>C_NTD</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>NextEra Energy Inc</t>
+          <t>CASH</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>143,395</t>
+          <t>267,442,084</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>5.29%</t>
+          <t>3.66%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>NOW US</t>
+          <t>SO US</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>ServiceNow Inc</t>
+          <t>南方公司</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>70,230</t>
+          <t>77,365</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -755,22 +755,22 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>SO US</t>
+          <t>NOW US</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>南方公司</t>
+          <t>ServiceNow Inc</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>77,365</t>
+          <t>70,230</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.14%</t>
+          <t>3.11%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>3.09%</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.88%</t>
+          <t>2.89%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>2.56%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>2.13%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>1.90%</t>
         </is>
       </c>
     </row>
@@ -946,24 +946,24 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.77%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>ETR US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>安特吉公司</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>9,440</t>
+          <t>31,398</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -975,17 +975,17 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>ETR US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>安特吉公司</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>31,398</t>
+          <t>9,440</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.48%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.47%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.40%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.39%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.24%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.17%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.07%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.75%</t>
+          <t>0.76%</t>
         </is>
       </c>
     </row>
@@ -1293,34 +1293,12 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>1,372,664</t>
+          <t>1,303,597</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.60%</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>RDI_USD</t>
-        </is>
-      </c>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>RECEIVABLES FOR DISPOSAL OF INVESTMENTS</t>
-        </is>
-      </c>
-      <c r="C53" s="4" t="inlineStr">
-        <is>
-          <t>-69,067</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr">
-        <is>
-          <t>0.00%</t>
+          <t>0.56%</t>
         </is>
       </c>
     </row>
